--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484837_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484837_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.4607</v>
+        <v>4.5691</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1005</v>
+        <v>3.3412</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3602</v>
+        <v>1.2279</v>
       </c>
       <c r="G2" t="n">
         <v>2.9632</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4143</v>
+        <v>1.5227</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0104</v>
+        <v>1.251</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4039</v>
+        <v>0.2716</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1055</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3232</v>
+        <v>4.2362</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5041</v>
+        <v>3.232</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8191000000000001</v>
+        <v>1.0043</v>
       </c>
       <c r="G3" t="n">
         <v>-0.9206</v>
@@ -688,13 +688,13 @@
         <v>1.887</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1874</v>
+        <v>1.1004</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3267</v>
+        <v>1.0545</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1393</v>
+        <v>0.0459</v>
       </c>
       <c r="V3" t="n">
         <v>4.0564</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5894</v>
+        <v>2.2867</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.04</v>
+        <v>-1.5843</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6294</v>
+        <v>3.871</v>
       </c>
       <c r="G4" t="n">
         <v>-0.9355</v>
@@ -766,13 +766,13 @@
         <v>4.3401</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6871</v>
+        <v>1.3844</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3884</v>
+        <v>0.8441</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2987</v>
+        <v>0.5403</v>
       </c>
       <c r="V4" t="n">
         <v>1.4604</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>J. ARTIGUES DANOBEITIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5509</v>
+        <v>1.9507</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5509</v>
+        <v>1.1182</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.8326</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5509</v>
+        <v>-0.6585</v>
       </c>
       <c r="H5" t="n">
-        <v>0.317</v>
+        <v>0.45</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2339</v>
+        <v>-1.1085</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5509</v>
+        <v>0.6141</v>
       </c>
       <c r="K5" t="n">
-        <v>0.317</v>
+        <v>0.5971</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2339</v>
+        <v>0.017</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.2727</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.1471</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-1.1256</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.2644</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.6581</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.6927</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.0347</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. ENGUIX TORMO</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4128</v>
+        <v>1.5509</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0077</v>
+        <v>1.5509</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4205</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6563</v>
+        <v>1.5509</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4132</v>
+        <v>0.317</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0695</v>
+        <v>1.2339</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.1572</v>
+        <v>1.5509</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5447</v>
+        <v>0.317</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7019</v>
+        <v>1.2339</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4991</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1315</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3676</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2644</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5142</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3195</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1947</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.7095</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.9813</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DAÑOBEITIA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9509</v>
+        <v>1.2805</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9509</v>
+        <v>0.7947</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.4858</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9509</v>
+        <v>2.8275</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9509</v>
+        <v>2.678</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.1495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9509</v>
+        <v>2.7035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9509</v>
+        <v>2.6624</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.124</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.0157</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.1083</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0218</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0.1669</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>J. ARTIGUES DAÑOBEITIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.832</v>
+        <v>0.9509</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3462</v>
+        <v>0.9509</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4858</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8275</v>
+        <v>0.9509</v>
       </c>
       <c r="H8" t="n">
-        <v>2.678</v>
+        <v>0.9509</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1495</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7035</v>
+        <v>0.9509</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6624</v>
+        <v>0.9509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.124</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0157</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1083</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6372</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4703</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1669</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ARTIGUES DANOBEITIA</t>
+          <t>H. ENGUIX TORMO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.509</v>
+        <v>0.4359</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0325</v>
+        <v>-0.8259</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5416</v>
+        <v>1.2618</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6585</v>
+        <v>-1.6563</v>
       </c>
       <c r="H9" t="n">
-        <v>0.45</v>
+        <v>0.4132</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1085</v>
+        <v>-2.0695</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6141</v>
+        <v>-1.1572</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5971</v>
+        <v>0.5447</v>
       </c>
       <c r="L9" t="n">
-        <v>0.017</v>
+        <v>-1.7019</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.2727</v>
+        <v>-0.4991</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1471</v>
+        <v>-0.1315</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1256</v>
+        <v>-0.3676</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.1887</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2644</v>
+        <v>2.4531</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7836</v>
+        <v>1.5374</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.458</v>
+        <v>1.5014</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3256</v>
+        <v>0.0359</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1245</v>
+        <v>-1.7095</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.9813</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1245</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9369</v>
+        <v>0.1311</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5118</v>
+        <v>-0.1138</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4252</v>
+        <v>0.245</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3751</v>
+        <v>-0.7435</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1628</v>
+        <v>-0.3498</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2123</v>
+        <v>-0.3937</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6496</v>
+        <v>-0.4617</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6496</v>
+        <v>0.0823</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7256</v>
+        <v>-0.2819</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1628</v>
+        <v>0.1941</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5628</v>
+        <v>-0.476</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.241</v>
+        <v>0.4331</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.164</v>
+        <v>0.3478</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.077</v>
+        <v>0.0853</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3018</v>
+        <v>-0.1245</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2455</v>
+        <v>-0.2656</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2259</v>
+        <v>-3.2325</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0196</v>
+        <v>2.9669</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7435</v>
+        <v>-1.9925</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3498</v>
+        <v>-1.6223</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3937</v>
+        <v>-0.3702</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4617</v>
+        <v>-1.8944</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-2.0434</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0823</v>
+        <v>0.1489</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2819</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1941</v>
+        <v>0.4211</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.476</v>
+        <v>-0.5191</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5661</v>
+        <v>3.5853</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9435</v>
+        <v>0.3418</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7642</v>
+        <v>0.4358</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1793</v>
+        <v>-0.094</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1245</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1245</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8472</v>
+        <v>-0.7988</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6554</v>
+        <v>-0.453</v>
       </c>
       <c r="F12" t="n">
-        <v>2.8082</v>
+        <v>-0.3458</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9925</v>
+        <v>-1.3751</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6223</v>
+        <v>-0.1628</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3702</v>
+        <v>-1.2123</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8944</v>
+        <v>-0.6496</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.0434</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1489</v>
+        <v>-0.6496</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.7256</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4211</v>
+        <v>-0.1628</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5191</v>
+        <v>-0.5628</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5096</v>
+        <v>0.3774</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.5853</v>
+        <v>0.3774</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.2398</v>
+        <v>-0.1029</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9871</v>
+        <v>-0.1052</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2527</v>
+        <v>0.0024</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1245</v>
+        <v>0.3018</v>
       </c>
       <c r="W12" t="n">
         <v>0.3018</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4263</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0257</v>
+        <v>-2.665</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.267</v>
+        <v>-2.065</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7587</v>
+        <v>-0.6</v>
       </c>
       <c r="G13" t="n">
         <v>-3.8009</v>
@@ -1468,13 +1468,13 @@
         <v>1.6983</v>
       </c>
       <c r="S13" t="n">
-        <v>1.643</v>
+        <v>1.0037</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7288</v>
+        <v>0.9308</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0858</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6226</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.72</v>
+        <v>-5.1841</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.9487</v>
+        <v>-3.5186</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7713</v>
+        <v>-1.6655</v>
       </c>
       <c r="G14" t="n">
         <v>-4.3056</v>
@@ -1546,13 +1546,13 @@
         <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6596</v>
+        <v>-0.1237</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4703</v>
+        <v>-0.0403</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1893</v>
+        <v>-0.0835</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.853599999999996</v>
+        <v>8.4785</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.236399999999999</v>
+        <v>-0.8051999999999997</v>
       </c>
       <c r="F15" t="n">
-        <v>9.09</v>
+        <v>9.283999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>-8.096</v>
@@ -1597,16 +1597,16 @@
         <v>-12.6625</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9285999999999999</v>
+        <v>0.928599999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4.870000000000001</v>
+        <v>4.869999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>-3.9413</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.0252</v>
+        <v>-9.025199999999998</v>
       </c>
       <c r="N15" t="n">
         <v>-0.3034</v>
@@ -1615,25 +1615,25 @@
         <v>-8.721499999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>7.548000000000001</v>
+        <v>7.547999999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-14.1525</v>
       </c>
       <c r="R15" t="n">
-        <v>21.7005</v>
+        <v>21.70050000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>5.941300000000001</v>
+        <v>7.566299999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>5.4599</v>
+        <v>6.8908</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4813999999999999</v>
+        <v>0.6752</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4605</v>
+        <v>1.460499999999999</v>
       </c>
       <c r="W15" t="n">
         <v>5.527500000000001</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6978</v>
+        <v>4.5553</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1938</v>
+        <v>2.681</v>
       </c>
       <c r="F16" t="n">
-        <v>1.504</v>
+        <v>1.8743</v>
       </c>
       <c r="G16" t="n">
         <v>3.3552</v>
@@ -1702,13 +1702,13 @@
         <v>1.3209</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7895</v>
+        <v>0.068</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6808</v>
+        <v>-0.1936</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1087</v>
+        <v>0.2616</v>
       </c>
       <c r="V16" t="n">
         <v>0.9434</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0272</v>
+        <v>3.2449</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9426</v>
+        <v>1.8452</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0846</v>
+        <v>1.3997</v>
       </c>
       <c r="G17" t="n">
         <v>3.6462</v>
@@ -1780,13 +1780,13 @@
         <v>1.3209</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0529</v>
+        <v>0.1648</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3803</v>
+        <v>0.2829</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4332</v>
+        <v>-0.1181</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8672</v>
+        <v>1.5709</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2159</v>
+        <v>-1.5339</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0831</v>
+        <v>3.1048</v>
       </c>
       <c r="G18" t="n">
         <v>1.674</v>
@@ -1858,13 +1858,13 @@
         <v>2.4531</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6371</v>
+        <v>-0.9333</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1511</v>
+        <v>-0.469</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.486</v>
+        <v>-0.4643</v>
       </c>
       <c r="V18" t="n">
         <v>0.6415999999999999</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1133</v>
+        <v>-0.1397</v>
       </c>
       <c r="E20" t="n">
         <v>-0.264</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1507</v>
+        <v>0.1243</v>
       </c>
       <c r="G20" t="n">
         <v>-0.1421</v>
@@ -2014,13 +2014,13 @@
         <v>0.1887</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0288</v>
+        <v>0.0024</v>
       </c>
       <c r="T20" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1464</v>
+        <v>0.1199</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.405</v>
+        <v>-0.3065</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4536</v>
+        <v>-0.131</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8586</v>
+        <v>-0.1755</v>
       </c>
       <c r="G21" t="n">
         <v>1.4354</v>
@@ -2092,13 +2092,13 @@
         <v>2.6418</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4256</v>
+        <v>-1.3271</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5625</v>
+        <v>-0.0221</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.988</v>
+        <v>-1.3049</v>
       </c>
       <c r="V21" t="n">
         <v>-1.547</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.703</v>
+        <v>-0.6056</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4326</v>
+        <v>0.53</v>
       </c>
       <c r="F22" t="n">
         <v>-1.1356</v>
@@ -2170,10 +2170,10 @@
         <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5073</v>
+        <v>-0.4099</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2352</v>
+        <v>-0.1377</v>
       </c>
       <c r="U22" t="n">
         <v>-0.2722</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. ANZULUNI</t>
+          <t>A. QUERALT-LORTZING VILLANUEVA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2696</v>
+        <v>-2.7891</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7397</v>
+        <v>-2.1267</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4701</v>
+        <v>-0.6624</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8068</v>
+        <v>0.002</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0776</v>
+        <v>-0.2082</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2709</v>
+        <v>0.2102</v>
       </c>
       <c r="J23" t="n">
-        <v>1.005</v>
+        <v>1.4601</v>
       </c>
       <c r="K23" t="n">
-        <v>2.0558</v>
+        <v>1.3367</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.0509</v>
+        <v>0.1234</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1982</v>
+        <v>-1.458</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9782</v>
+        <v>-1.5448</v>
       </c>
       <c r="O23" t="n">
-        <v>0.78</v>
+        <v>0.0868</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.3966</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6.2271</v>
+        <v>-3.9627</v>
       </c>
       <c r="R23" t="n">
-        <v>2.8305</v>
+        <v>0.3774</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9618</v>
+        <v>0.2096</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.4329</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3282</v>
+        <v>-0.2234</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.5846</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8488</v>
+        <v>-0.0569</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4904</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. QUERALT-LORTZING VILLANUEVA</t>
+          <t>M. ANZULUNI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3079</v>
+        <v>-3.4493</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5421</v>
+        <v>-3.2269</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7659</v>
+        <v>-0.2224</v>
       </c>
       <c r="G24" t="n">
-        <v>0.002</v>
+        <v>0.8068</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2082</v>
+        <v>1.0776</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2102</v>
+        <v>-0.2709</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4601</v>
+        <v>1.005</v>
       </c>
       <c r="K24" t="n">
-        <v>1.3367</v>
+        <v>2.0558</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1234</v>
+        <v>-1.0509</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.458</v>
+        <v>-0.1982</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5448</v>
+        <v>-0.9782</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0868</v>
+        <v>0.78</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.5853</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9627</v>
+        <v>-6.2271</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3774</v>
+        <v>2.8305</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6907</v>
+        <v>-0.2179</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0175</v>
+        <v>0.1464</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3268</v>
+        <v>-0.3643</v>
       </c>
       <c r="V24" t="n">
-        <v>0.5846</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.0569</v>
+        <v>1.8488</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6415999999999999</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.5569</v>
+        <v>-3.6748</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.2697</v>
+        <v>-2.4646</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2872</v>
+        <v>-1.2102</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2007</v>
@@ -2404,13 +2404,13 @@
         <v>0.5661</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7901</v>
+        <v>-0.9079</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1205</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9105</v>
+        <v>-0.8335</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.6646</v>
+        <v>-5.5352</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.2871</v>
+        <v>-5.6051</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3774</v>
+        <v>0.0699</v>
       </c>
       <c r="G26" t="n">
         <v>-1.1319</v>
@@ -2482,13 +2482,13 @@
         <v>2.0757</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3249</v>
+        <v>-1.1955</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6097</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.7153</v>
+        <v>-1.2679</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9434</v>
@@ -2515,16 +2515,16 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.1111</v>
+        <v>-6.812099999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.978899999999999</v>
+        <v>-9.978999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>1.867799999999999</v>
+        <v>3.1669</v>
       </c>
       <c r="G27" t="n">
-        <v>7.811400000000001</v>
+        <v>7.811399999999999</v>
       </c>
       <c r="H27" t="n">
         <v>-5.6111</v>
@@ -2539,7 +2539,7 @@
         <v>-0.72</v>
       </c>
       <c r="L27" t="n">
-        <v>9.522500000000001</v>
+        <v>9.522499999999999</v>
       </c>
       <c r="M27" t="n">
         <v>-0.9909000000000002</v>
@@ -2560,13 +2560,13 @@
         <v>14.1525</v>
       </c>
       <c r="S27" t="n">
-        <v>-5.8461</v>
+        <v>-4.5468</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.07999999999999974</v>
+        <v>-0.07979999999999994</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.7661</v>
+        <v>-4.4671</v>
       </c>
       <c r="V27" t="n">
         <v>-1.585</v>
